--- a/open-world/config/excel/航图.xlsx
+++ b/open-world/config/excel/航图.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="1" r:id="Red556d5a77724251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="航区" sheetId="2" r:id="R2aa44ed555bc44ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残页" sheetId="3" r:id="R465e8c1102cd4cd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="4" r:id="R29a8953260af4a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="5" r:id="R9c3dc837492f4f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="1" r:id="R54b8759545ae4f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="航区" sheetId="2" r:id="R59c7d7ce7ccc4756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残页" sheetId="3" r:id="R97eefb7340f34ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="4" r:id="R556137e508ba4004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="5" r:id="R4bb8434231674f6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -874,7 +874,7 @@
         <x:v>[]</x:v>
       </x:c>
       <x:c r="P7" s="1" t="str">
-        <x:v>武器、鞋子；海克斯偏向 贴身绞杀</x:v>
+        <x:v>武器、鞋子；巢穴三段战利品</x:v>
       </x:c>
       <x:c r="Q7" s="1" t="str">
         <x:v>{"xp":760,"gold":55,"material":6,"shards":0,"shardChance":0.6,"rep":15}</x:v>
@@ -945,7 +945,7 @@
         <x:v>[]</x:v>
       </x:c>
       <x:c r="P8" s="1" t="str">
-        <x:v>武器、鞋子；海克斯偏向 贴身绞杀</x:v>
+        <x:v>衣服、头盔；巢穴三段战利品</x:v>
       </x:c>
       <x:c r="Q8" s="1" t="str">
         <x:v>{"xp":759,"gold":55,"material":6,"shards":0,"shardChance":0.6,"rep":15}</x:v>
@@ -1016,7 +1016,7 @@
         <x:v>[]</x:v>
       </x:c>
       <x:c r="P9" s="1" t="str">
-        <x:v>武器、鞋子；海克斯偏向 贴身绞杀</x:v>
+        <x:v>项链、戒指；巢穴三段战利品</x:v>
       </x:c>
       <x:c r="Q9" s="1" t="str">
         <x:v>{"xp":656,"gold":47,"material":5,"shards":0,"shardChance":0.6,"rep":15}</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>[]</x:v>
       </x:c>
       <x:c r="P17" s="1" t="str">
-        <x:v>武器、鞋子；海克斯偏向 贴身绞杀</x:v>
+        <x:v>武器、鞋子；巢穴三段战利品</x:v>
       </x:c>
       <x:c r="Q17" s="1" t="str">
         <x:v>{"xp":40599,"gold":877,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
@@ -1655,7 +1655,7 @@
         <x:v>[]</x:v>
       </x:c>
       <x:c r="P18" s="1" t="str">
-        <x:v>武器、鞋子；海克斯偏向 贴身绞杀</x:v>
+        <x:v>衣服、头盔；巢穴三段战利品</x:v>
       </x:c>
       <x:c r="Q18" s="1" t="str">
         <x:v>{"xp":40599,"gold":877,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
@@ -1726,7 +1726,7 @@
         <x:v>[]</x:v>
       </x:c>
       <x:c r="P19" s="1" t="str">
-        <x:v>武器、鞋子；海克斯偏向 贴身绞杀</x:v>
+        <x:v>项链、戒指；巢穴三段战利品</x:v>
       </x:c>
       <x:c r="Q19" s="1" t="str">
         <x:v>{"xp":40599,"gold":877,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
@@ -2034,9 +2034,2641 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="1" t="str">
+        <x:v>forge-story-1</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="str">
+        <x:v>输能溯源</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="str">
+        <x:v>这根管原来给工坊供能。现在阀门改了，能量全往岛外走。</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="str">
+        <x:v>story-forge-1</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="str">
+        <x:v>ss-map-forge</x:v>
+      </x:c>
+      <x:c r="H24" s="1" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I24" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="str">
+        <x:v>["forge-story-2","forge-story-3","forge-nest-1"]</x:v>
+      </x:c>
+      <x:c r="K24" s="1" t="str">
+        <x:v>{"col":0,"row":1}</x:v>
+      </x:c>
+      <x:c r="L24" s="1" t="str">
+        <x:v>["ss-c03-t01","ss-c03-t02"]</x:v>
+      </x:c>
+      <x:c r="M24" s="1" t="str">
+        <x:v>[{"task":"ss-c03-t01","seq":1,"op":"interact","key":"object:0","label":"查看输能管上的改装记录","hint":"{verb}{thing}{part}","map":"ss-map-forge","landmark":"clue","prop":"ss-prop-pipe","world_fact":true,"zone":"ow-forge-z2"},{"task":"ss-c03-t02","seq":1,"op":"battle","key":"wave","label":"清掉一号冷却阀旁的搬运机","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-forge","landmark":"valve-1","point_index":0,"point_count":1,"prop":"ss-prop-valve","count":2,"enemies":["ss-mon-ore-loader"],"world_fact":false,"zone":"ow-forge-z3"},{"task":"ss-c03-t02","seq":2,"op":"interact","key":"object:0","label":"重开一号冷却阀","hint":"{verb}{thing}{part}","map":"ss-map-forge","landmark":"valve-1","point_index":0,"point_count":1,"prop":"ss-prop-valve","world_fact":false,"zone":"ow-forge-z3"},{"task":"ss-c03-t02","seq":3,"op":"battle","key":"wave","label":"清掉二号冷却阀旁的搬运机","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-forge","landmark":"valve-2","point_index":0,"point_count":1,"prop":"ss-prop-valve","count":2,"enemies":["ss-mon-ore-loader"],"world_fact":false,"zone":"ow-forge-z3"},{"task":"ss-c03-t02","seq":4,"op":"interact","key":"object:1","label":"重开二号冷却阀","hint":"{verb}{thing}{part}","map":"ss-map-forge","landmark":"valve-2","point_index":0,"point_count":1,"prop":"ss-prop-valve","world_fact":false,"zone":"ow-forge-z3"}]</x:v>
+      </x:c>
+      <x:c r="N24" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O24" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P24" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q24" s="1" t="str">
+        <x:v>{"xp":58455,"gold":1170,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R24" s="1"/>
+      <x:c r="S24" s="1"/>
+      <x:c r="T24" s="1"/>
+      <x:c r="U24" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V24" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W24" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="1" t="str">
+        <x:v>forge-story-2</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="str">
+        <x:v>夺回控制</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="str">
+        <x:v>炉顶的铳手看得远，矿道里是重甲搬运机。两边都能到控制台。</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="str">
+        <x:v>story-forge-2</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="str">
+        <x:v>ss-map-forge</x:v>
+      </x:c>
+      <x:c r="H25" s="1" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I25" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="str">
+        <x:v>["forge-story-1","forge-nest-2"]</x:v>
+      </x:c>
+      <x:c r="K25" s="1" t="str">
+        <x:v>{"col":1,"row":1}</x:v>
+      </x:c>
+      <x:c r="L25" s="1" t="str">
+        <x:v>["ss-c03-t03"]</x:v>
+      </x:c>
+      <x:c r="M25" s="1" t="str">
+        <x:v>[{"task":"ss-c03-t03","seq":1,"op":"choose","key":"route","label":"在分岔口选炉顶或矿道","hint":"走到分岔口，选一条进攻路线","map":"ss-map-forge","landmark":"route-fork","world_fact":false,"zone":"ow-forge-z5"},{"task":"ss-c03-t03","seq":2,"op":"route_battle","key":"wave","label":"清掉所选路线的守卫","map":"ss-map-forge","landmark":"route-a","count":3,"world_fact":false,"zone":"ow-forge-z5"}]</x:v>
+      </x:c>
+      <x:c r="N25" s="1" t="str">
+        <x:v>[{"task":"ss-c03-t03","slot":"a","id":"roof","name":"炉顶检修路","landmark":"route-a","enemies":["ss-mon-dusk-gunner","ss-mon-dusk-weaver"],"goal":"清除3名远程守卫","risk":"铳手和织隙者都在远处出手，借管线掩护逐个接近。"},{"task":"ss-c03-t03","slot":"b","id":"mine","name":"矿道运输路","landmark":"route-b","enemies":["ss-elite-forge-overseer","ss-mon-ore-loader"],"goal":"清除3名重装守卫","risk":"炉甲压阵机是精英，冲撞很疼；侧身躲开再反击。"}]</x:v>
+      </x:c>
+      <x:c r="O25" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P25" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q25" s="1" t="str">
+        <x:v>{"xp":58455,"gold":1170,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R25" s="1"/>
+      <x:c r="S25" s="1"/>
+      <x:c r="T25" s="1"/>
+      <x:c r="U25" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V25" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W25" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="1" t="str">
+        <x:v>forge-story-3</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="str">
+        <x:v>守住岛心</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="str">
+        <x:v>我需要岛心稳定的这段时间。敌人压进来，稳定就会中断。</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="str">
+        <x:v>story-forge-3</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="str">
+        <x:v>ss-map-forge</x:v>
+      </x:c>
+      <x:c r="H26" s="1" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I26" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="str">
+        <x:v>["forge-story-1","forge-nest-3"]</x:v>
+      </x:c>
+      <x:c r="K26" s="1" t="str">
+        <x:v>{"col":1,"row":2}</x:v>
+      </x:c>
+      <x:c r="L26" s="1" t="str">
+        <x:v>["ss-c03-t04","ss-c03-n02"]</x:v>
+      </x:c>
+      <x:c r="M26" s="1" t="str">
+        <x:v>[{"task":"ss-c03-t04","seq":1,"op":"defend","key":"wave","label":"守住岛心稳定器","hint":"守住{thing}：打倒 {need} 个敌人{part}","map":"ss-map-forge","landmark":"objective","prop":"ss-prop-core","count":4,"enemies":["ss-mon-dusk-blade","ss-mon-dusk-weaver"],"defense":"engine","world_fact":false,"zone":"ow-forge-z6"},{"task":"ss-c03-n02","seq":1,"op":"gate","key":"gate-forge","label":"打开炉心隔热门","map":"ss-map-forge","landmark":"gate","world_fact":true,"zone":"ow-forge-z6","gate":"gate-forge"}]</x:v>
+      </x:c>
+      <x:c r="N26" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O26" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P26" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q26" s="1" t="str">
+        <x:v>{"xp":58455,"gold":1170,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R26" s="1"/>
+      <x:c r="S26" s="1"/>
+      <x:c r="T26" s="1"/>
+      <x:c r="U26" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V26" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W26" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="1" t="str">
+        <x:v>forge-nest-1</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="str">
+        <x:v>输能检修道</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="str">
+        <x:v>沿检修道切断搬运机的增援，回收输能零件。</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="str">
+        <x:v>field-forge-1</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="str">
+        <x:v>ss-dg-forge-1-1</x:v>
+      </x:c>
+      <x:c r="H27" s="1" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="str">
+        <x:v>["forge-story-1","forge-nest-2","forge-hunt"]</x:v>
+      </x:c>
+      <x:c r="K27" s="1" t="str">
+        <x:v>{"col":1,"row":0}</x:v>
+      </x:c>
+      <x:c r="L27" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M27" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N27" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O27" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P27" s="1" t="str">
+        <x:v>武器、鞋子；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q27" s="1" t="str">
+        <x:v>{"xp":75991,"gold":1521,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R27" s="1"/>
+      <x:c r="S27" s="1"/>
+      <x:c r="T27" s="1"/>
+      <x:c r="U27" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V27" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="1" t="str">
+        <x:v>forge-nest-2</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="str">
+        <x:v>冷却井</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="str">
+        <x:v>穿过冷却井的三段通道，夺回阀门控制。</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="str">
+        <x:v>field-forge-2</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="str">
+        <x:v>ss-dg-forge-2-1</x:v>
+      </x:c>
+      <x:c r="H28" s="1" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="str">
+        <x:v>["forge-story-2","forge-nest-1","forge-nest-3","forge-tide"]</x:v>
+      </x:c>
+      <x:c r="K28" s="1" t="str">
+        <x:v>{"col":2,"row":1}</x:v>
+      </x:c>
+      <x:c r="L28" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M28" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N28" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O28" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P28" s="1" t="str">
+        <x:v>衣服、头盔；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q28" s="1" t="str">
+        <x:v>{"xp":75991,"gold":1521,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R28" s="1"/>
+      <x:c r="S28" s="1"/>
+      <x:c r="T28" s="1"/>
+      <x:c r="U28" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V28" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="1" t="str">
+        <x:v>forge-nest-3</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="str">
+        <x:v>炉心遗构</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="str">
+        <x:v>清理炉心遗构，让封存的设备重新见光。</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="str">
+        <x:v>field-forge-3</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="str">
+        <x:v>ss-dg-forge-3-1</x:v>
+      </x:c>
+      <x:c r="H29" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I29" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="str">
+        <x:v>["forge-story-3","forge-nest-2","forge-treasure"]</x:v>
+      </x:c>
+      <x:c r="K29" s="1" t="str">
+        <x:v>{"col":2,"row":2}</x:v>
+      </x:c>
+      <x:c r="L29" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M29" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N29" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O29" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P29" s="1" t="str">
+        <x:v>项链、戒指；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q29" s="1" t="str">
+        <x:v>{"xp":75991,"gold":1521,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R29" s="1"/>
+      <x:c r="S29" s="1"/>
+      <x:c r="T29" s="1"/>
+      <x:c r="U29" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V29" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="1" t="str">
+        <x:v>forge-hunt</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="str">
+        <x:v>hunt</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="str">
+        <x:v>脱轨装载场</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="str">
+        <x:v>击败稀有精英，留意本场机关：落石、涨潮或引雷桩。</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="str">
+        <x:v>hub-forge-hunt</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="str">
+        <x:v>ss-dg-forge-1-3</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I30" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="str">
+        <x:v>["forge-nest-1","forge-gate"]</x:v>
+      </x:c>
+      <x:c r="K30" s="1" t="str">
+        <x:v>{"col":3,"row":0}</x:v>
+      </x:c>
+      <x:c r="L30" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M30" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N30" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O30" s="1" t="str">
+        <x:v>["生命星晶","赤炉配方"]</x:v>
+      </x:c>
+      <x:c r="P30" s="1" t="str">
+        <x:v>武器；稀有精英掉落</x:v>
+      </x:c>
+      <x:c r="Q30" s="1" t="str">
+        <x:v>{"xp":37021,"gold":741,"material":28,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R30" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S30" s="1"/>
+      <x:c r="T30" s="1" t="str">
+        <x:v>"forge-resist"</x:v>
+      </x:c>
+      <x:c r="U30" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V30" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W30" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="1" t="str">
+        <x:v>forge-tide</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="str">
+        <x:v>tide</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="str">
+        <x:v>泄压前庭</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="str">
+        <x:v>守住泄压前庭的信标，挡下四波追兵。</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="str">
+        <x:v>hub-forge-tide</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="str">
+        <x:v>ss-dg-forge-2-1</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I31" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="str">
+        <x:v>["forge-nest-2","forge-gate"]</x:v>
+      </x:c>
+      <x:c r="K31" s="1" t="str">
+        <x:v>{"col":3,"row":1}</x:v>
+      </x:c>
+      <x:c r="L31" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M31" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N31" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O31" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P31" s="1" t="str">
+        <x:v>材料、经验；海克斯事件掉落</x:v>
+      </x:c>
+      <x:c r="Q31" s="1" t="str">
+        <x:v>{"xp":58455,"gold":1170,"material":45,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R31" s="1"/>
+      <x:c r="S31" s="1"/>
+      <x:c r="T31" s="1"/>
+      <x:c r="U31" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V31" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W31" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="1" t="str">
+        <x:v>forge-treasure</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="str">
+        <x:v>废炉货仓</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="str">
+        <x:v>在警报结束前打开五箱，取回工坊的库存。</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="str">
+        <x:v>hub-forge-treasure</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="str">
+        <x:v>ss-dg-forge-3-2</x:v>
+      </x:c>
+      <x:c r="H32" s="1" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I32" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="str">
+        <x:v>["forge-nest-3","forge-gate"]</x:v>
+      </x:c>
+      <x:c r="K32" s="1" t="str">
+        <x:v>{"col":3,"row":2}</x:v>
+      </x:c>
+      <x:c r="L32" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M32" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N32" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O32" s="1" t="str">
+        <x:v>["生命星晶"]</x:v>
+      </x:c>
+      <x:c r="P32" s="1" t="str">
+        <x:v>图样、配方、残页、潮晶</x:v>
+      </x:c>
+      <x:c r="Q32" s="1" t="str">
+        <x:v>{"xp":31176,"gold":624,"material":24,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R32" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S32" s="1"/>
+      <x:c r="T32" s="1"/>
+      <x:c r="U32" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V32" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W32" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="1" t="str">
+        <x:v>forge-gate</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="str">
+        <x:v>gate</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="str">
+        <x:v>击败采能机</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="str">
+        <x:v>它的聚束沿着钳口射出。躲开地面的方向线，别把退路让给炉火。</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="str">
+        <x:v>hub-forge-gate</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="str">
+        <x:v>ss-map-boss-3</x:v>
+      </x:c>
+      <x:c r="H33" s="1" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I33" s="1" t="str">
+        <x:v>[3,5]</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="str">
+        <x:v>["forge-hunt","forge-tide","forge-treasure"]</x:v>
+      </x:c>
+      <x:c r="K33" s="1" t="str">
+        <x:v>{"col":4,"row":1}</x:v>
+      </x:c>
+      <x:c r="L33" s="1" t="str">
+        <x:v>["ss-c03-t05"]</x:v>
+      </x:c>
+      <x:c r="M33" s="1" t="str">
+        <x:v>[{"task":"ss-c03-t05","seq":1,"op":"boss","key":"boss","label":"击败岛心采能机·掘星者","map":"ss-map-boss-3","world_fact":true,"zone":"ow-forge-z6"}]</x:v>
+      </x:c>
+      <x:c r="N33" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O33" s="1" t="str">
+        <x:v>["关口首通伙伴","解锁地区外观","开启霜镜航区"]</x:v>
+      </x:c>
+      <x:c r="P33" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q33" s="1" t="str">
+        <x:v>{"xp":46764,"gold":936,"material":36,"shards":1,"rep":40}</x:v>
+      </x:c>
+      <x:c r="R33" s="1"/>
+      <x:c r="S33" s="1" t="str">
+        <x:v>"200331"</x:v>
+      </x:c>
+      <x:c r="T33" s="1"/>
+      <x:c r="U33" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V33" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W33" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="1" t="str">
+        <x:v>frost-story-1</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="str">
+        <x:v>冻舰搜查</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="str">
+        <x:v>冰封的是记录室，不是里面的时间。别把旧日期当成今天的消息。</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="str">
+        <x:v>story-frost-1</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="str">
+        <x:v>ss-map-frost</x:v>
+      </x:c>
+      <x:c r="H34" s="1" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I34" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J34" s="1" t="str">
+        <x:v>["frost-story-2","frost-story-3","frost-nest-1"]</x:v>
+      </x:c>
+      <x:c r="K34" s="1" t="str">
+        <x:v>{"col":0,"row":1}</x:v>
+      </x:c>
+      <x:c r="L34" s="1" t="str">
+        <x:v>["ss-c04-t01","ss-c04-t02"]</x:v>
+      </x:c>
+      <x:c r="M34" s="1" t="str">
+        <x:v>[{"task":"ss-c04-t01","seq":1,"op":"interact","key":"object:0","label":"读取西侧冻舰的记录","hint":"{verb}{thing}{part}","map":"ss-map-frost","landmark":"clue-b","point_index":0,"point_count":1,"prop":"ss-prop-log","world_fact":true,"zone":"ow-frost-z2"},{"task":"ss-c04-t01","seq":2,"op":"interact","key":"object:1","label":"读取中间冻舰的记录","hint":"{verb}{thing}{part}","map":"ss-map-frost","landmark":"clue-b","point_index":0,"point_count":1,"prop":"ss-prop-log","world_fact":false,"zone":"ow-frost-z2"},{"task":"ss-c04-t01","seq":3,"op":"interact","key":"object:2","label":"读取东侧冻舰的记录","hint":"{verb}{thing}{part}","map":"ss-map-frost","landmark":"clue-b","point_index":0,"point_count":1,"prop":"ss-prop-log","world_fact":false,"zone":"ow-frost-z2"},{"task":"ss-c04-t02","seq":1,"op":"battle","key":"wave","label":"清掉一号观测镜旁的守卫","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-frost","landmark":"device-1","point_index":0,"point_count":1,"prop":"ss-prop-observatory","count":2,"enemies":["ss-mon-frozen-watch"],"world_fact":false,"zone":"ow-frost-z3"},{"task":"ss-c04-t02","seq":2,"op":"interact","key":"object:0","label":"唤醒一号观测镜","hint":"{verb}{thing}{part}","map":"ss-map-frost","landmark":"device-1","point_index":0,"point_count":1,"prop":"ss-prop-observatory","world_fact":false,"zone":"ow-frost-z3"},{"task":"ss-c04-t02","seq":3,"op":"battle","key":"wave","label":"清掉二号观测镜旁的守卫","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-frost","landmark":"device-2","point_index":0,"point_count":1,"prop":"ss-prop-observatory","count":2,"enemies":["ss-mon-frozen-watch"],"world_fact":false,"zone":"ow-frost-z3"},{"task":"ss-c04-t02","seq":4,"op":"interact","key":"object:1","label":"唤醒二号观测镜","hint":"{verb}{thing}{part}","map":"ss-map-frost","landmark":"device-2","point_index":0,"point_count":1,"prop":"ss-prop-observatory","world_fact":false,"zone":"ow-frost-z3"}]</x:v>
+      </x:c>
+      <x:c r="N34" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O34" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P34" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q34" s="1" t="str">
+        <x:v>{"xp":175005,"gold":1980,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R34" s="1"/>
+      <x:c r="S34" s="1"/>
+      <x:c r="T34" s="1"/>
+      <x:c r="U34" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V34" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W34" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="1" t="str">
+        <x:v>frost-story-2</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="str">
+        <x:v>进入舰桥</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="str">
+        <x:v>内部有霜锁卫士，外壳路上有铳手放冷枪。选一条，我们在星盘室会合。</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="str">
+        <x:v>story-frost-2</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="str">
+        <x:v>ss-map-frost</x:v>
+      </x:c>
+      <x:c r="H35" s="1" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I35" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J35" s="1" t="str">
+        <x:v>["frost-story-1","frost-nest-2"]</x:v>
+      </x:c>
+      <x:c r="K35" s="1" t="str">
+        <x:v>{"col":1,"row":1}</x:v>
+      </x:c>
+      <x:c r="L35" s="1" t="str">
+        <x:v>["ss-c04-t03","ss-c04-n02"]</x:v>
+      </x:c>
+      <x:c r="M35" s="1" t="str">
+        <x:v>[{"task":"ss-c04-t03","seq":1,"op":"choose","key":"route","label":"在分岔口选内部舰桥或外壳通道","hint":"走到分岔口，选一条进攻路线","map":"ss-map-frost","landmark":"route-fork","world_fact":false,"zone":"ow-frost-z5"},{"task":"ss-c04-t03","seq":2,"op":"route_battle","key":"wave","label":"清掉所选路线的守卫","map":"ss-map-frost","landmark":"route-a","count":3,"world_fact":false,"zone":"ow-frost-z5"},{"task":"ss-c04-n02","seq":1,"op":"gate","key":"gate-frost","label":"打开冰封舱门","map":"ss-map-frost","landmark":"gate","world_fact":true,"zone":"ow-frost-z5","gate":"gate-frost"}]</x:v>
+      </x:c>
+      <x:c r="N35" s="1" t="str">
+        <x:v>[{"task":"ss-c04-t03","slot":"a","id":"bridge-deck","name":"内部舰桥","landmark":"route-a","enemies":["ss-elite-frost-lock","ss-mon-frozen-watch"],"goal":"清除3名甲板守卫","risk":"霜锁卫士是精英，会把你冻在原地；别被困在窄舱里。"},{"task":"ss-c04-t03","slot":"b","id":"outer-hull","name":"外壳通道","landmark":"route-b","enemies":["ss-mon-dusk-gunner","ss-mon-frost-hound"],"goal":"清除3名外壳巡兵","risk":"铳手放冷枪，巡猎兽会扑上来；先解决铳手。"}]</x:v>
+      </x:c>
+      <x:c r="O35" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P35" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q35" s="1" t="str">
+        <x:v>{"xp":175005,"gold":1980,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R35" s="1"/>
+      <x:c r="S35" s="1"/>
+      <x:c r="T35" s="1"/>
+      <x:c r="U35" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V35" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W35" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="1" t="str">
+        <x:v>frost-story-3</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="str">
+        <x:v>复原星图</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="str">
+        <x:v>这是保管人的印记。援航条款仍然有效，但开启记录不是开启归途。</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="str">
+        <x:v>story-frost-3</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="str">
+        <x:v>ss-map-frost</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I36" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J36" s="1" t="str">
+        <x:v>["frost-story-1","frost-nest-3"]</x:v>
+      </x:c>
+      <x:c r="K36" s="1" t="str">
+        <x:v>{"col":1,"row":2}</x:v>
+      </x:c>
+      <x:c r="L36" s="1" t="str">
+        <x:v>["ss-c04-t04"]</x:v>
+      </x:c>
+      <x:c r="M36" s="1" t="str">
+        <x:v>[{"task":"ss-c04-t04","seq":1,"op":"interact","key":"object:0","label":"用刻片校验星盘记录","hint":"{verb}{thing}{part}","map":"ss-map-frost","landmark":"objective","prop":"ss-prop-star-chart","world_fact":true,"zone":"ow-frost-z6"}]</x:v>
+      </x:c>
+      <x:c r="N36" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O36" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P36" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q36" s="1" t="str">
+        <x:v>{"xp":175005,"gold":1980,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R36" s="1"/>
+      <x:c r="S36" s="1"/>
+      <x:c r="T36" s="1"/>
+      <x:c r="U36" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V36" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W36" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="1" t="str">
+        <x:v>frost-nest-1</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="str">
+        <x:v>冻舰底舱</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="str">
+        <x:v>清理冻舰底舱，找回冰封船员留下的物资。</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="str">
+        <x:v>field-frost-1</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="str">
+        <x:v>ss-dg-frost-1-1</x:v>
+      </x:c>
+      <x:c r="H37" s="1" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I37" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J37" s="1" t="str">
+        <x:v>["frost-story-1","frost-nest-2","frost-hunt"]</x:v>
+      </x:c>
+      <x:c r="K37" s="1" t="str">
+        <x:v>{"col":1,"row":0}</x:v>
+      </x:c>
+      <x:c r="L37" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M37" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N37" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O37" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P37" s="1" t="str">
+        <x:v>武器、鞋子；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q37" s="1" t="str">
+        <x:v>{"xp":227506,"gold":2574,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R37" s="1"/>
+      <x:c r="S37" s="1"/>
+      <x:c r="T37" s="1"/>
+      <x:c r="U37" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V37" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="1" t="str">
+        <x:v>frost-nest-2</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="str">
+        <x:v>观测冰窟</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="str">
+        <x:v>穿过观测冰窟，拆掉巡守的阻截。</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="str">
+        <x:v>field-frost-2</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="str">
+        <x:v>ss-dg-frost-2-1</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I38" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J38" s="1" t="str">
+        <x:v>["frost-story-2","frost-nest-1","frost-nest-3","frost-tide"]</x:v>
+      </x:c>
+      <x:c r="K38" s="1" t="str">
+        <x:v>{"col":2,"row":1}</x:v>
+      </x:c>
+      <x:c r="L38" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M38" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N38" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O38" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P38" s="1" t="str">
+        <x:v>衣服、头盔；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q38" s="1" t="str">
+        <x:v>{"xp":227506,"gold":2574,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R38" s="1"/>
+      <x:c r="S38" s="1"/>
+      <x:c r="T38" s="1"/>
+      <x:c r="U38" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="1" t="str">
+        <x:v>frost-nest-3</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="str">
+        <x:v>星盘残室</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="str">
+        <x:v>走到星盘残室深处，取回旧航约的零件。</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="str">
+        <x:v>field-frost-3</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="str">
+        <x:v>ss-dg-frost-3-1</x:v>
+      </x:c>
+      <x:c r="H39" s="1" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I39" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="str">
+        <x:v>["frost-story-3","frost-nest-2","frost-treasure"]</x:v>
+      </x:c>
+      <x:c r="K39" s="1" t="str">
+        <x:v>{"col":2,"row":2}</x:v>
+      </x:c>
+      <x:c r="L39" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M39" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N39" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O39" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P39" s="1" t="str">
+        <x:v>项链、戒指；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q39" s="1" t="str">
+        <x:v>{"xp":227506,"gold":2574,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R39" s="1"/>
+      <x:c r="S39" s="1"/>
+      <x:c r="T39" s="1"/>
+      <x:c r="U39" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="1" t="str">
+        <x:v>frost-hunt</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="str">
+        <x:v>hunt</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="str">
+        <x:v>冰隙巡猎</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="str">
+        <x:v>击败稀有精英，留意本场机关：落石、涨潮或引雷桩。</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="str">
+        <x:v>hub-frost-hunt</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="str">
+        <x:v>ss-dg-frost-1-3</x:v>
+      </x:c>
+      <x:c r="H40" s="1" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I40" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J40" s="1" t="str">
+        <x:v>["frost-nest-1","frost-gate"]</x:v>
+      </x:c>
+      <x:c r="K40" s="1" t="str">
+        <x:v>{"col":3,"row":0}</x:v>
+      </x:c>
+      <x:c r="L40" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M40" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N40" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O40" s="1" t="str">
+        <x:v>["生命星晶","霜镜配方"]</x:v>
+      </x:c>
+      <x:c r="P40" s="1" t="str">
+        <x:v>武器；稀有精英掉落</x:v>
+      </x:c>
+      <x:c r="Q40" s="1" t="str">
+        <x:v>{"xp":110836,"gold":1254,"material":28,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R40" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S40" s="1"/>
+      <x:c r="T40" s="1" t="str">
+        <x:v>"frost-resist"</x:v>
+      </x:c>
+      <x:c r="U40" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W40" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="1" t="str">
+        <x:v>frost-tide</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="str">
+        <x:v>tide</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="str">
+        <x:v>观测站守夜</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="str">
+        <x:v>守住观测站信标，让四轮求援信号发出去。</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="str">
+        <x:v>hub-frost-tide</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="str">
+        <x:v>ss-dg-frost-2-1</x:v>
+      </x:c>
+      <x:c r="H41" s="1" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I41" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J41" s="1" t="str">
+        <x:v>["frost-nest-2","frost-gate"]</x:v>
+      </x:c>
+      <x:c r="K41" s="1" t="str">
+        <x:v>{"col":3,"row":1}</x:v>
+      </x:c>
+      <x:c r="L41" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M41" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N41" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O41" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P41" s="1" t="str">
+        <x:v>材料、经验；海克斯事件掉落</x:v>
+      </x:c>
+      <x:c r="Q41" s="1" t="str">
+        <x:v>{"xp":175005,"gold":1980,"material":45,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R41" s="1"/>
+      <x:c r="S41" s="1"/>
+      <x:c r="T41" s="1"/>
+      <x:c r="U41" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W41" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="1" t="str">
+        <x:v>frost-treasure</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="str">
+        <x:v>封冻储藏室</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="str">
+        <x:v>趁冰雾散开打开五箱，搜集遗失的记录。</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="str">
+        <x:v>hub-frost-treasure</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="str">
+        <x:v>ss-dg-frost-3-2</x:v>
+      </x:c>
+      <x:c r="H42" s="1" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I42" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J42" s="1" t="str">
+        <x:v>["frost-nest-3","frost-gate"]</x:v>
+      </x:c>
+      <x:c r="K42" s="1" t="str">
+        <x:v>{"col":3,"row":2}</x:v>
+      </x:c>
+      <x:c r="L42" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M42" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N42" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O42" s="1" t="str">
+        <x:v>["生命星晶"]</x:v>
+      </x:c>
+      <x:c r="P42" s="1" t="str">
+        <x:v>图样、配方、残页、潮晶</x:v>
+      </x:c>
+      <x:c r="Q42" s="1" t="str">
+        <x:v>{"xp":93336,"gold":1056,"material":24,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R42" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S42" s="1"/>
+      <x:c r="T42" s="1"/>
+      <x:c r="U42" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W42" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="1" t="str">
+        <x:v>frost-gate</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="str">
+        <x:v>gate</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="str">
+        <x:v>冻舰巡守</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="str">
+        <x:v>巡守把所有新信号都当成侵入。冰枪的发射方向和风雪范围都会先出现。</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="str">
+        <x:v>hub-frost-gate</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="str">
+        <x:v>ss-map-boss-4</x:v>
+      </x:c>
+      <x:c r="H43" s="1" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I43" s="1" t="str">
+        <x:v>[3,5]</x:v>
+      </x:c>
+      <x:c r="J43" s="1" t="str">
+        <x:v>["frost-hunt","frost-tide","frost-treasure"]</x:v>
+      </x:c>
+      <x:c r="K43" s="1" t="str">
+        <x:v>{"col":4,"row":1}</x:v>
+      </x:c>
+      <x:c r="L43" s="1" t="str">
+        <x:v>["ss-c04-t05"]</x:v>
+      </x:c>
+      <x:c r="M43" s="1" t="str">
+        <x:v>[{"task":"ss-c04-t05","seq":1,"op":"boss","key":"boss","label":"击败冻舰巡守·霜镜卫","map":"ss-map-boss-4","world_fact":true,"zone":"ow-frost-z6"}]</x:v>
+      </x:c>
+      <x:c r="N43" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O43" s="1" t="str">
+        <x:v>["关口首通伙伴","解锁地区外观","开启沉星航区"]</x:v>
+      </x:c>
+      <x:c r="P43" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q43" s="1" t="str">
+        <x:v>{"xp":140004,"gold":1584,"material":36,"shards":1,"rep":40}</x:v>
+      </x:c>
+      <x:c r="R43" s="1"/>
+      <x:c r="S43" s="1" t="str">
+        <x:v>"300571"</x:v>
+      </x:c>
+      <x:c r="T43" s="1"/>
+      <x:c r="U43" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W43" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="1" t="str">
+        <x:v>rift-story-1</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="str">
+        <x:v>要塞登陆</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="str">
+        <x:v>这里有前线军队，也有被带来的平民。我会给你明确位置，不让你靠猜测动手。</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="str">
+        <x:v>story-rift-1</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="str">
+        <x:v>ss-map-rift</x:v>
+      </x:c>
+      <x:c r="H44" s="1" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I44" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J44" s="1" t="str">
+        <x:v>["rift-story-2","rift-story-3","rift-nest-1"]</x:v>
+      </x:c>
+      <x:c r="K44" s="1" t="str">
+        <x:v>{"col":0,"row":1}</x:v>
+      </x:c>
+      <x:c r="L44" s="1" t="str">
+        <x:v>["ss-c05-t01","ss-c05-t02","ss-c05-n02"]</x:v>
+      </x:c>
+      <x:c r="M44" s="1" t="str">
+        <x:v>[{"task":"ss-c05-t01","seq":1,"op":"battle","key":"wave","label":"击退登陆点的裂隙守卫","hint":"打倒 {need} 个敌人","map":"ss-map-rift","landmark":"landing","count":3,"enemies":["ss-mon-rift-lurker","ss-mon-dusk-blade"],"world_fact":false,"zone":"ow-rift-z1"},{"task":"ss-c05-t02","seq":1,"op":"interact","key":"object:0","label":"核对老人的证词","hint":"{verb}{thing}{part}","map":"ss-map-rift","landmark":"clue-a","point_index":0,"point_count":1,"prop":"ss-prop-testimony","world_fact":true,"zone":"ow-rift-z2"},{"task":"ss-c05-t02","seq":2,"op":"interact","key":"object:1","label":"安顿工匠，记下他的证词","hint":"{verb}{thing}{part}","map":"ss-map-rift","landmark":"clue-b","point_index":0,"point_count":1,"prop":"ss-prop-refugee","world_fact":false,"zone":"ow-rift-z2"},{"task":"ss-c05-t02","seq":3,"op":"interact","key":"object:2","label":"拆阅母女托付的信","hint":"{verb}{thing}{part}","map":"ss-map-rift","landmark":"clue-c","point_index":0,"point_count":1,"prop":"ss-prop-letter","world_fact":false,"zone":"ow-rift-z2"}]</x:v>
+      </x:c>
+      <x:c r="N44" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O44" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P44" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q44" s="1" t="str">
+        <x:v>{"xp":275580,"gold":3285,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R44" s="1"/>
+      <x:c r="S44" s="1"/>
+      <x:c r="T44" s="1"/>
+      <x:c r="U44" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W44" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="1" t="str">
+        <x:v>rift-story-2</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="str">
+        <x:v>穿过前哨</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="str">
+        <x:v>炮台路能先处理铳手，裂隙路由潜猎者巡守。两边都能走到供能厅。</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="str">
+        <x:v>story-rift-2</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="str">
+        <x:v>ss-map-rift</x:v>
+      </x:c>
+      <x:c r="H45" s="1" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I45" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J45" s="1" t="str">
+        <x:v>["rift-story-1","rift-nest-2"]</x:v>
+      </x:c>
+      <x:c r="K45" s="1" t="str">
+        <x:v>{"col":1,"row":1}</x:v>
+      </x:c>
+      <x:c r="L45" s="1" t="str">
+        <x:v>["ss-c05-t03"]</x:v>
+      </x:c>
+      <x:c r="M45" s="1" t="str">
+        <x:v>[{"task":"ss-c05-t03","seq":1,"op":"choose","key":"route","label":"在分岔口选炮台或裂隙通道","hint":"走到分岔口，选一条进攻路线","map":"ss-map-rift","landmark":"route-fork","world_fact":false,"zone":"ow-rift-z3"},{"task":"ss-c05-t03","seq":2,"op":"route_battle","key":"wave","label":"清掉所选路线的守卫","map":"ss-map-rift","landmark":"route-a","count":3,"world_fact":false,"zone":"ow-rift-z3"}]</x:v>
+      </x:c>
+      <x:c r="N45" s="1" t="str">
+        <x:v>[{"task":"ss-c05-t03","slot":"a","id":"battery","name":"炮台通道","landmark":"route-a","enemies":["ss-mon-dusk-gunner","ss-mon-dusk-weaver"],"goal":"清除3名炮台守卫","risk":"铳手和织隙者火力集中，先打离你最近的那个。"},{"task":"ss-c05-t03","slot":"b","id":"rift-path","name":"裂隙通道","landmark":"route-b","enemies":["ss-elite-rift-hunter","ss-mon-rift-lurker"],"goal":"清除3名裂隙巡兵","risk":"裂界猎兵是精英，潜猎者会从侧面偷袭；留意身边的动静。"}]</x:v>
+      </x:c>
+      <x:c r="O45" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P45" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q45" s="1" t="str">
+        <x:v>{"xp":275580,"gold":3285,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R45" s="1"/>
+      <x:c r="S45" s="1"/>
+      <x:c r="T45" s="1"/>
+      <x:c r="U45" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W45" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="1" t="str">
+        <x:v>rift-story-3</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="str">
+        <x:v>断开界桥供能</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="str">
+        <x:v>按编号断开供能。不要把仍在使用的撤离装置和军用供能器混在一起。</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="str">
+        <x:v>story-rift-3</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="str">
+        <x:v>ss-map-rift</x:v>
+      </x:c>
+      <x:c r="H46" s="1" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I46" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="str">
+        <x:v>["rift-story-1","rift-nest-3"]</x:v>
+      </x:c>
+      <x:c r="K46" s="1" t="str">
+        <x:v>{"col":1,"row":2}</x:v>
+      </x:c>
+      <x:c r="L46" s="1" t="str">
+        <x:v>["ss-c05-t04"]</x:v>
+      </x:c>
+      <x:c r="M46" s="1" t="str">
+        <x:v>[{"task":"ss-c05-t04","seq":1,"op":"clear_camp","key":"ow-rift-camp-5-10","label":"清掉一号供能器旁的守卫","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-rift","landmark":"device-1","point_index":0,"point_count":1,"prop":"ss-prop-supply","world_fact":true,"zone":"ow-rift-z5","camp":"ow-rift-camp-5-10"},{"task":"ss-c05-t04","seq":2,"op":"interact","key":"object:0","label":"断开一号供能器","hint":"{verb}{thing}{part}","map":"ss-map-rift","landmark":"device-1","point_index":0,"point_count":1,"prop":"ss-prop-supply","world_fact":false,"zone":"ow-rift-z5"},{"task":"ss-c05-t04","seq":3,"op":"clear_camp","key":"ow-rift-camp-5-34","label":"清掉二号供能器旁的守卫","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-rift","landmark":"device-2","point_index":0,"point_count":1,"prop":"ss-prop-supply","world_fact":true,"zone":"ow-rift-z5","camp":"ow-rift-camp-5-34"},{"task":"ss-c05-t04","seq":4,"op":"interact","key":"object:1","label":"断开二号供能器","hint":"{verb}{thing}{part}","map":"ss-map-rift","landmark":"device-2","point_index":0,"point_count":1,"prop":"ss-prop-supply","world_fact":false,"zone":"ow-rift-z5"},{"task":"ss-c05-t04","seq":5,"op":"clear_camp","key":"ow-rift-camp-5-23","label":"清掉三号供能器旁的守卫","hint":"打倒{thing}旁的 {need} 个敌人{part}","map":"ss-map-rift","landmark":"device-3","point_index":0,"point_count":1,"prop":"ss-prop-supply","world_fact":true,"zone":"ow-rift-z5","camp":"ow-rift-camp-5-23"},{"task":"ss-c05-t04","seq":6,"op":"interact","key":"object:2","label":"断开三号供能器","hint":"{verb}{thing}{part}","map":"ss-map-rift","landmark":"device-3","point_index":0,"point_count":1,"prop":"ss-prop-supply","world_fact":false,"zone":"ow-rift-z5"}]</x:v>
+      </x:c>
+      <x:c r="N46" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O46" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P46" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q46" s="1" t="str">
+        <x:v>{"xp":275580,"gold":3285,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R46" s="1"/>
+      <x:c r="S46" s="1"/>
+      <x:c r="T46" s="1"/>
+      <x:c r="U46" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W46" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="1" t="str">
+        <x:v>rift-nest-1</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="str">
+        <x:v>沉星密仓</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="str">
+        <x:v>穿过沉星密仓，给撤离队找回补给。</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="str">
+        <x:v>field-rift-1</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="str">
+        <x:v>ss-dg-rift-1-1</x:v>
+      </x:c>
+      <x:c r="H47" s="1" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I47" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J47" s="1" t="str">
+        <x:v>["rift-story-1","rift-nest-2","rift-hunt"]</x:v>
+      </x:c>
+      <x:c r="K47" s="1" t="str">
+        <x:v>{"col":1,"row":0}</x:v>
+      </x:c>
+      <x:c r="L47" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M47" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N47" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O47" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P47" s="1" t="str">
+        <x:v>武器、鞋子；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q47" s="1" t="str">
+        <x:v>{"xp":358254,"gold":4270,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R47" s="1"/>
+      <x:c r="S47" s="1"/>
+      <x:c r="T47" s="1"/>
+      <x:c r="U47" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="1" t="str">
+        <x:v>rift-nest-2</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="str">
+        <x:v>裂隙炮台</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="str">
+        <x:v>逐段清除炮台守卫，打开滩头的退路。</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="str">
+        <x:v>field-rift-2</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="str">
+        <x:v>ss-dg-rift-2-1</x:v>
+      </x:c>
+      <x:c r="H48" s="1" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I48" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="str">
+        <x:v>["rift-story-2","rift-nest-1","rift-nest-3","rift-tide"]</x:v>
+      </x:c>
+      <x:c r="K48" s="1" t="str">
+        <x:v>{"col":2,"row":1}</x:v>
+      </x:c>
+      <x:c r="L48" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M48" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N48" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O48" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P48" s="1" t="str">
+        <x:v>衣服、头盔；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q48" s="1" t="str">
+        <x:v>{"xp":358254,"gold":4270,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R48" s="1"/>
+      <x:c r="S48" s="1"/>
+      <x:c r="T48" s="1"/>
+      <x:c r="U48" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V48" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="1" t="str">
+        <x:v>rift-nest-3</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="str">
+        <x:v>界桥地窖</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="str">
+        <x:v>深入界桥地窖，夺回供能器旁的物资。</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="str">
+        <x:v>field-rift-3</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="str">
+        <x:v>ss-dg-rift-3-1</x:v>
+      </x:c>
+      <x:c r="H49" s="1" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I49" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="str">
+        <x:v>["rift-story-3","rift-nest-2","rift-treasure"]</x:v>
+      </x:c>
+      <x:c r="K49" s="1" t="str">
+        <x:v>{"col":2,"row":2}</x:v>
+      </x:c>
+      <x:c r="L49" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M49" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N49" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O49" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P49" s="1" t="str">
+        <x:v>项链、戒指；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q49" s="1" t="str">
+        <x:v>{"xp":358254,"gold":4270,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R49" s="1"/>
+      <x:c r="S49" s="1"/>
+      <x:c r="T49" s="1"/>
+      <x:c r="U49" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V49" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="1" t="str">
+        <x:v>rift-hunt</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="str">
+        <x:v>hunt</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="str">
+        <x:v>前哨追猎</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="str">
+        <x:v>击败稀有精英，留意本场机关：落石、涨潮或引雷桩。</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="str">
+        <x:v>hub-rift-hunt</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="str">
+        <x:v>ss-dg-rift-1-3</x:v>
+      </x:c>
+      <x:c r="H50" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I50" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="str">
+        <x:v>["rift-nest-1","rift-gate"]</x:v>
+      </x:c>
+      <x:c r="K50" s="1" t="str">
+        <x:v>{"col":3,"row":0}</x:v>
+      </x:c>
+      <x:c r="L50" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M50" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N50" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O50" s="1" t="str">
+        <x:v>["生命星晶","沉星配方"]</x:v>
+      </x:c>
+      <x:c r="P50" s="1" t="str">
+        <x:v>武器；稀有精英掉落</x:v>
+      </x:c>
+      <x:c r="Q50" s="1" t="str">
+        <x:v>{"xp":174534,"gold":2080,"material":28,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R50" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S50" s="1"/>
+      <x:c r="T50" s="1" t="str">
+        <x:v>"rift-resist"</x:v>
+      </x:c>
+      <x:c r="U50" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V50" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W50" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="1" t="str">
+        <x:v>rift-tide</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="str">
+        <x:v>tide</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="str">
+        <x:v>滩头守灯</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="str">
+        <x:v>守住滩头信标，撑过四波追兵。</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="str">
+        <x:v>hub-rift-tide</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="str">
+        <x:v>ss-dg-rift-2-1</x:v>
+      </x:c>
+      <x:c r="H51" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I51" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J51" s="1" t="str">
+        <x:v>["rift-nest-2","rift-gate"]</x:v>
+      </x:c>
+      <x:c r="K51" s="1" t="str">
+        <x:v>{"col":3,"row":1}</x:v>
+      </x:c>
+      <x:c r="L51" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M51" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N51" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O51" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P51" s="1" t="str">
+        <x:v>材料、经验；海克斯事件掉落</x:v>
+      </x:c>
+      <x:c r="Q51" s="1" t="str">
+        <x:v>{"xp":275580,"gold":3285,"material":45,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R51" s="1"/>
+      <x:c r="S51" s="1"/>
+      <x:c r="T51" s="1"/>
+      <x:c r="U51" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V51" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W51" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="1" t="str">
+        <x:v>rift-treasure</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="str">
+        <x:v>撤离物资库</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="str">
+        <x:v>赶在封锁前打开五箱，找回被扣的补给。</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="str">
+        <x:v>hub-rift-treasure</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="str">
+        <x:v>ss-dg-rift-3-2</x:v>
+      </x:c>
+      <x:c r="H52" s="1" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I52" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="str">
+        <x:v>["rift-nest-3","rift-gate"]</x:v>
+      </x:c>
+      <x:c r="K52" s="1" t="str">
+        <x:v>{"col":3,"row":2}</x:v>
+      </x:c>
+      <x:c r="L52" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M52" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N52" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O52" s="1" t="str">
+        <x:v>["生命星晶"]</x:v>
+      </x:c>
+      <x:c r="P52" s="1" t="str">
+        <x:v>图样、配方、残页、潮晶</x:v>
+      </x:c>
+      <x:c r="Q52" s="1" t="str">
+        <x:v>{"xp":146976,"gold":1752,"material":24,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R52" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S52" s="1"/>
+      <x:c r="T52" s="1"/>
+      <x:c r="U52" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V52" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W52" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="1" t="str">
+        <x:v>rift-gate</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="str">
+        <x:v>gate</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="str">
+        <x:v>击败前线督军</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="str">
+        <x:v>他在祭台上接着另一端。离开干扰区，看到仪式蓄力就处理召来的敌人。</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="str">
+        <x:v>hub-rift-gate</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="str">
+        <x:v>ss-map-boss-5</x:v>
+      </x:c>
+      <x:c r="H53" s="1" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I53" s="1" t="str">
+        <x:v>[3,5]</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="str">
+        <x:v>["rift-hunt","rift-tide","rift-treasure"]</x:v>
+      </x:c>
+      <x:c r="K53" s="1" t="str">
+        <x:v>{"col":4,"row":1}</x:v>
+      </x:c>
+      <x:c r="L53" s="1" t="str">
+        <x:v>["ss-c05-t05"]</x:v>
+      </x:c>
+      <x:c r="M53" s="1" t="str">
+        <x:v>[{"task":"ss-c05-t05","seq":1,"op":"boss","key":"boss","label":"击败裂隙督军·乌洛","map":"ss-map-boss-5","world_fact":true,"zone":"ow-rift-z6"}]</x:v>
+      </x:c>
+      <x:c r="N53" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O53" s="1" t="str">
+        <x:v>["关口首通伙伴","解锁地区外观","开启龙眠航区"]</x:v>
+      </x:c>
+      <x:c r="P53" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q53" s="1" t="str">
+        <x:v>{"xp":220464,"gold":2628,"material":36,"shards":1,"rep":40}</x:v>
+      </x:c>
+      <x:c r="R53" s="1"/>
+      <x:c r="S53" s="1" t="str">
+        <x:v>"400105"</x:v>
+      </x:c>
+      <x:c r="T53" s="1"/>
+      <x:c r="U53" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V53" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W53" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="1" t="str">
+        <x:v>dragon-story-1</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="str">
+        <x:v>龙裔会盟</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="str">
+        <x:v>契约认可应答者，也要求有人共同担责。你带来的记录足以让六岛重新会盟。</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="str">
+        <x:v>story-dragon-1</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="str">
+        <x:v>ss-map-dragon</x:v>
+      </x:c>
+      <x:c r="H54" s="1" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I54" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J54" s="1" t="str">
+        <x:v>["dragon-story-2","dragon-story-3","dragon-nest-1"]</x:v>
+      </x:c>
+      <x:c r="K54" s="1" t="str">
+        <x:v>{"col":0,"row":1}</x:v>
+      </x:c>
+      <x:c r="L54" s="1" t="str">
+        <x:v>["ss-c06-t01","ss-c06-t02"]</x:v>
+      </x:c>
+      <x:c r="M54" s="1" t="str">
+        <x:v>[{"task":"ss-c06-t02","seq":1,"op":"battle","key":"wave","label":"击退失控的旧航网巡守","hint":"打倒 {need} 个敌人","map":"ss-map-dragon","landmark":"objective","count":3,"enemies":["ss-mon-bone-sentinel","ss-mon-oath-acolyte","ss-elite-oath-keeper"],"world_fact":false,"zone":"ow-dragon-z2"}]</x:v>
+      </x:c>
+      <x:c r="N54" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O54" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P54" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q54" s="1" t="str">
+        <x:v>{"xp":500580,"gold":5040,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R54" s="1"/>
+      <x:c r="S54" s="1"/>
+      <x:c r="T54" s="1"/>
+      <x:c r="U54" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V54" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W54" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="1" t="str">
+        <x:v>dragon-story-2</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="str">
+        <x:v>进入航网中枢</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="str">
+        <x:v>祭道上是旧约巡守，机库里是舰团兵。我们得选一条能保住退路的。</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="str">
+        <x:v>story-dragon-2</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="str">
+        <x:v>ss-map-dragon</x:v>
+      </x:c>
+      <x:c r="H55" s="1" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I55" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J55" s="1" t="str">
+        <x:v>["dragon-story-1","dragon-nest-2"]</x:v>
+      </x:c>
+      <x:c r="K55" s="1" t="str">
+        <x:v>{"col":1,"row":1}</x:v>
+      </x:c>
+      <x:c r="L55" s="1" t="str">
+        <x:v>["ss-c06-t03","ss-c06-n02"]</x:v>
+      </x:c>
+      <x:c r="M55" s="1" t="str">
+        <x:v>[{"task":"ss-c06-t03","seq":1,"op":"choose","key":"route","label":"在分岔口选旧祭道或机库","hint":"走到分岔口，选一条进攻路线","map":"ss-map-dragon","landmark":"route-fork","world_fact":false,"zone":"ow-dragon-z3"},{"task":"ss-c06-t03","seq":2,"op":"route_battle","key":"wave","label":"清掉所选路线的守卫","map":"ss-map-dragon","landmark":"route-a","count":3,"world_fact":false,"zone":"ow-dragon-z3"},{"task":"ss-c06-n02","seq":1,"op":"gate","key":"gate-dragon","label":"打开航网屏障","map":"ss-map-dragon","landmark":"gate","world_fact":true,"zone":"ow-dragon-z6","gate":"gate-dragon"}]</x:v>
+      </x:c>
+      <x:c r="N55" s="1" t="str">
+        <x:v>[{"task":"ss-c06-t03","slot":"a","id":"oath-road","name":"旧祭道","landmark":"route-a","enemies":["ss-elite-oath-keeper","ss-mon-oath-acolyte"],"goal":"清除3名旧航巡守","risk":"龙骨执令者是精英，侍仪会给它加护；先打断护持。"},{"task":"ss-c06-t03","slot":"b","id":"hangar","name":"机库通道","landmark":"route-b","enemies":["ss-mon-dusk-gunner","ss-mon-dusk-weaver"],"goal":"清除3名舰团守卫","risk":"铳手和织隙者都在远处出手，别一次引来太多。"}]</x:v>
+      </x:c>
+      <x:c r="O55" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P55" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q55" s="1" t="str">
+        <x:v>{"xp":500580,"gold":5040,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R55" s="1"/>
+      <x:c r="S55" s="1"/>
+      <x:c r="T55" s="1"/>
+      <x:c r="U55" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V55" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W55" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="1" t="str">
+        <x:v>dragon-story-3</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="str">
+        <x:v>story</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="str">
+        <x:v>稳定航网节点</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="str">
+        <x:v>一次稳住一个节点。没人守住范围，或敌人压入，稳定就不会增长。</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="str">
+        <x:v>story-dragon-3</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="str">
+        <x:v>ss-map-dragon</x:v>
+      </x:c>
+      <x:c r="H56" s="1" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I56" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J56" s="1" t="str">
+        <x:v>["dragon-story-1","dragon-nest-3"]</x:v>
+      </x:c>
+      <x:c r="K56" s="1" t="str">
+        <x:v>{"col":1,"row":2}</x:v>
+      </x:c>
+      <x:c r="L56" s="1" t="str">
+        <x:v>["ss-c06-t04"]</x:v>
+      </x:c>
+      <x:c r="M56" s="1" t="str">
+        <x:v>[{"task":"ss-c06-t04","seq":1,"op":"defend","key":"wave","label":"启动并守住一号节点","hint":"守住{thing}：打倒 {need} 个敌人{part}","map":"ss-map-dragon","landmark":"device-1","point_index":0,"point_count":1,"prop":"ss-prop-node","count":3,"enemies":["ss-mon-dusk-blade","ss-mon-dusk-weaver"],"defense":"engine","world_fact":false,"zone":"ow-dragon-z5"},{"task":"ss-c06-t04","seq":2,"op":"defend","key":"wave","label":"启动并守住二号节点","hint":"守住{thing}：打倒 {need} 个敌人{part}","map":"ss-map-dragon","landmark":"device-2","point_index":0,"point_count":1,"prop":"ss-prop-node","count":3,"enemies":["ss-mon-dusk-blade","ss-mon-dusk-weaver"],"defense":"engine","world_fact":false,"zone":"ow-dragon-z5"},{"task":"ss-c06-t04","seq":3,"op":"defend","key":"wave","label":"启动并守住三号节点","hint":"守住{thing}：打倒 {need} 个敌人{part}","map":"ss-map-dragon","landmark":"device-3","point_index":0,"point_count":1,"prop":"ss-prop-node","count":3,"enemies":["ss-mon-dusk-blade","ss-mon-dusk-weaver"],"defense":"engine","world_fact":false,"zone":"ow-dragon-z5"}]</x:v>
+      </x:c>
+      <x:c r="N56" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O56" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P56" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q56" s="1" t="str">
+        <x:v>{"xp":500580,"gold":5040,"material":45,"shards":0,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R56" s="1"/>
+      <x:c r="S56" s="1"/>
+      <x:c r="T56" s="1"/>
+      <x:c r="U56" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V56" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W56" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="1" t="str">
+        <x:v>dragon-nest-1</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="str">
+        <x:v>龙骨洞穴</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="str">
+        <x:v>沿龙骨洞穴深入，清除封住旧路的巡守。</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="str">
+        <x:v>field-dragon-1</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="str">
+        <x:v>ss-dg-dragon-1-1</x:v>
+      </x:c>
+      <x:c r="H57" s="1" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I57" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J57" s="1" t="str">
+        <x:v>["dragon-story-1","dragon-nest-2","dragon-hunt"]</x:v>
+      </x:c>
+      <x:c r="K57" s="1" t="str">
+        <x:v>{"col":1,"row":0}</x:v>
+      </x:c>
+      <x:c r="L57" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M57" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N57" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O57" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P57" s="1" t="str">
+        <x:v>武器、鞋子；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q57" s="1" t="str">
+        <x:v>{"xp":650754,"gold":6552,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R57" s="1"/>
+      <x:c r="S57" s="1"/>
+      <x:c r="T57" s="1"/>
+      <x:c r="U57" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V57" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="1" t="str">
+        <x:v>dragon-nest-2</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="str">
+        <x:v>旧祭遗堂</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="str">
+        <x:v>走过旧祭遗堂，找回应答者留存的器物。</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="str">
+        <x:v>field-dragon-2</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="str">
+        <x:v>ss-dg-dragon-2-1</x:v>
+      </x:c>
+      <x:c r="H58" s="1" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I58" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J58" s="1" t="str">
+        <x:v>["dragon-story-2","dragon-nest-1","dragon-nest-3","dragon-tide"]</x:v>
+      </x:c>
+      <x:c r="K58" s="1" t="str">
+        <x:v>{"col":2,"row":1}</x:v>
+      </x:c>
+      <x:c r="L58" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M58" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N58" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O58" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P58" s="1" t="str">
+        <x:v>衣服、头盔；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q58" s="1" t="str">
+        <x:v>{"xp":650754,"gold":6552,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R58" s="1"/>
+      <x:c r="S58" s="1"/>
+      <x:c r="T58" s="1"/>
+      <x:c r="U58" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V58" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="1" t="str">
+        <x:v>dragon-nest-3</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="str">
+        <x:v>nest</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="str">
+        <x:v>航网机库</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="str">
+        <x:v>清理航网机库，让停摆的设备重新运转。</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="str">
+        <x:v>field-dragon-3</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="str">
+        <x:v>ss-dg-dragon-3-1</x:v>
+      </x:c>
+      <x:c r="H59" s="1" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I59" s="1" t="str">
+        <x:v>[5,8]</x:v>
+      </x:c>
+      <x:c r="J59" s="1" t="str">
+        <x:v>["dragon-story-3","dragon-nest-2","dragon-treasure"]</x:v>
+      </x:c>
+      <x:c r="K59" s="1" t="str">
+        <x:v>{"col":2,"row":2}</x:v>
+      </x:c>
+      <x:c r="L59" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M59" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N59" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O59" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P59" s="1" t="str">
+        <x:v>项链、戒指；巢穴三段战利品</x:v>
+      </x:c>
+      <x:c r="Q59" s="1" t="str">
+        <x:v>{"xp":650754,"gold":6552,"material":58,"shards":0,"shardChance":0.6,"rep":15}</x:v>
+      </x:c>
+      <x:c r="R59" s="1"/>
+      <x:c r="S59" s="1"/>
+      <x:c r="T59" s="1"/>
+      <x:c r="U59" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V59" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W59" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="1" t="str">
+        <x:v>dragon-hunt</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="str">
+        <x:v>hunt</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="str">
+        <x:v>失控看守机</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="str">
+        <x:v>击败稀有精英，留意本场机关：落石、涨潮或引雷桩。</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="str">
+        <x:v>hub-dragon-hunt</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="str">
+        <x:v>ss-dg-dragon-1-3</x:v>
+      </x:c>
+      <x:c r="H60" s="1" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I60" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J60" s="1" t="str">
+        <x:v>["dragon-nest-1","dragon-gate"]</x:v>
+      </x:c>
+      <x:c r="K60" s="1" t="str">
+        <x:v>{"col":3,"row":0}</x:v>
+      </x:c>
+      <x:c r="L60" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M60" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N60" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O60" s="1" t="str">
+        <x:v>["生命星晶","龙眠配方"]</x:v>
+      </x:c>
+      <x:c r="P60" s="1" t="str">
+        <x:v>武器；稀有精英掉落</x:v>
+      </x:c>
+      <x:c r="Q60" s="1" t="str">
+        <x:v>{"xp":317034,"gold":3192,"material":28,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R60" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S60" s="1"/>
+      <x:c r="T60" s="1" t="str">
+        <x:v>"dragon-resist"</x:v>
+      </x:c>
+      <x:c r="U60" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V60" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W60" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="1" t="str">
+        <x:v>dragon-tide</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="str">
+        <x:v>tide</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="str">
+        <x:v>誓约守灯</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="str">
+        <x:v>守住誓约信标，挡住四波失控巡守。</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="str">
+        <x:v>hub-dragon-tide</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="str">
+        <x:v>ss-dg-dragon-2-1</x:v>
+      </x:c>
+      <x:c r="H61" s="1" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I61" s="1" t="str">
+        <x:v>[4,6]</x:v>
+      </x:c>
+      <x:c r="J61" s="1" t="str">
+        <x:v>["dragon-nest-2","dragon-gate"]</x:v>
+      </x:c>
+      <x:c r="K61" s="1" t="str">
+        <x:v>{"col":3,"row":1}</x:v>
+      </x:c>
+      <x:c r="L61" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M61" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N61" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O61" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="P61" s="1" t="str">
+        <x:v>材料、经验；海克斯事件掉落</x:v>
+      </x:c>
+      <x:c r="Q61" s="1" t="str">
+        <x:v>{"xp":500580,"gold":5040,"material":45,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R61" s="1"/>
+      <x:c r="S61" s="1"/>
+      <x:c r="T61" s="1"/>
+      <x:c r="U61" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V61" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W61" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="1" t="str">
+        <x:v>dragon-treasure</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="str">
+        <x:v>旧约藏室</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="str">
+        <x:v>在封存倒计时结束前打开五箱旧约物资。</x:v>
+      </x:c>
+      <x:c r="F62" s="1" t="str">
+        <x:v>hub-dragon-treasure</x:v>
+      </x:c>
+      <x:c r="G62" s="1" t="str">
+        <x:v>ss-dg-dragon-3-2</x:v>
+      </x:c>
+      <x:c r="H62" s="1" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I62" s="1" t="str">
+        <x:v>[2,4]</x:v>
+      </x:c>
+      <x:c r="J62" s="1" t="str">
+        <x:v>["dragon-nest-3","dragon-gate"]</x:v>
+      </x:c>
+      <x:c r="K62" s="1" t="str">
+        <x:v>{"col":3,"row":2}</x:v>
+      </x:c>
+      <x:c r="L62" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="M62" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N62" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O62" s="1" t="str">
+        <x:v>["生命星晶"]</x:v>
+      </x:c>
+      <x:c r="P62" s="1" t="str">
+        <x:v>图样、配方、残页、潮晶</x:v>
+      </x:c>
+      <x:c r="Q62" s="1" t="str">
+        <x:v>{"xp":266976,"gold":2688,"material":24,"shards":0,"shardChance":0.6,"rep":5}</x:v>
+      </x:c>
+      <x:c r="R62" s="1" t="str">
+        <x:v>"lifeCrystal"</x:v>
+      </x:c>
+      <x:c r="S62" s="1"/>
+      <x:c r="T62" s="1"/>
+      <x:c r="U62" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V62" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W62" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="1" t="str">
+        <x:v>dragon-gate</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="str">
+        <x:v>gate</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="str">
+        <x:v>暮界提督</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="str">
+        <x:v>我的人没有时间继续等。我知道这座桥的代价，也知道不接它会失去什么。</x:v>
+      </x:c>
+      <x:c r="F63" s="1" t="str">
+        <x:v>hub-dragon-gate</x:v>
+      </x:c>
+      <x:c r="G63" s="1" t="str">
+        <x:v>ss-map-boss-6</x:v>
+      </x:c>
+      <x:c r="H63" s="1" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I63" s="1" t="str">
+        <x:v>[3,5]</x:v>
+      </x:c>
+      <x:c r="J63" s="1" t="str">
+        <x:v>["dragon-hunt","dragon-tide","dragon-treasure"]</x:v>
+      </x:c>
+      <x:c r="K63" s="1" t="str">
+        <x:v>{"col":4,"row":1}</x:v>
+      </x:c>
+      <x:c r="L63" s="1" t="str">
+        <x:v>["ss-c06-t05"]</x:v>
+      </x:c>
+      <x:c r="M63" s="1" t="str">
+        <x:v>[{"task":"ss-c06-t05","seq":1,"op":"boss","key":"boss","label":"击败暮界提督·维洛","map":"ss-map-boss-6","world_fact":true,"zone":"ow-dragon-z6"}]</x:v>
+      </x:c>
+      <x:c r="N63" s="1" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="O63" s="1" t="str">
+        <x:v>["关口首通伙伴","解锁地区外观","开启深潮"]</x:v>
+      </x:c>
+      <x:c r="P63" s="1" t="str">
+        <x:v>装备与首通奖励</x:v>
+      </x:c>
+      <x:c r="Q63" s="1" t="str">
+        <x:v>{"xp":400464,"gold":4032,"material":36,"shards":1,"rep":40}</x:v>
+      </x:c>
+      <x:c r="R63" s="1"/>
+      <x:c r="S63" s="1" t="str">
+        <x:v>"400108"</x:v>
+      </x:c>
+      <x:c r="T63" s="1"/>
+      <x:c r="U63" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V63" t="str">
+        <x:v>{"hp":1,"attack":1}</x:v>
+      </x:c>
+      <x:c r="W63" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad49fc506589485c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd825a80caf384b4e"/>
 </x:worksheet>
 </file>
 
@@ -2131,7 +4763,7 @@
         <x:v>[15,21]</x:v>
       </x:c>
       <x:c r="D6" s="1" t="str">
-        <x:v>locked</x:v>
+        <x:v>open</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2145,7 +4777,7 @@
         <x:v>[21,27]</x:v>
       </x:c>
       <x:c r="D7" s="1" t="str">
-        <x:v>locked</x:v>
+        <x:v>open</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2159,7 +4791,7 @@
         <x:v>[27,32]</x:v>
       </x:c>
       <x:c r="D8" s="1" t="str">
-        <x:v>locked</x:v>
+        <x:v>open</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2173,7 +4805,7 @@
         <x:v>[32,37]</x:v>
       </x:c>
       <x:c r="D9" s="1" t="str">
-        <x:v>locked</x:v>
+        <x:v>open</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
